--- a/artfynd/A 10495-2026 artfynd.xlsx
+++ b/artfynd/A 10495-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97730472</v>
+        <v>98553592</v>
       </c>
       <c r="B2" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2779</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1201, Sm</t>
+          <t>Restad, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492737.5262541074</v>
+        <v>492694</v>
       </c>
       <c r="R2" t="n">
-        <v>6430482.004447373</v>
+        <v>6430457</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,16 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>lind</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,62 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97730474</v>
+        <v>98554094</v>
       </c>
       <c r="B3" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>805</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Turner) Th.Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1201, Sm</t>
+          <t>Restad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492777.8173766575</v>
+        <v>492835</v>
       </c>
       <c r="R3" t="n">
-        <v>6430456.503164577</v>
+        <v>6430319</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,16 +862,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -916,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97730473</v>
+        <v>98554101</v>
       </c>
       <c r="B4" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,37 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1201, Sm</t>
+          <t>Restad, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492726.8735681881</v>
+        <v>492716</v>
       </c>
       <c r="R4" t="n">
-        <v>6430461.363470236</v>
+        <v>6430313</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,16 +968,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1032,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98553592</v>
+        <v>98554106</v>
       </c>
       <c r="B5" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492693.9580591197</v>
+        <v>492726</v>
       </c>
       <c r="R5" t="n">
-        <v>6430456.655794837</v>
+        <v>6430289</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,21 +1061,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1131,7 +1077,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>lind</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98553631</v>
+        <v>98554109</v>
       </c>
       <c r="B6" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492668.5771783059</v>
+        <v>492707</v>
       </c>
       <c r="R6" t="n">
-        <v>6430508.618014718</v>
+        <v>6430345</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,21 +1167,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,7 +1183,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1274,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98553627</v>
+        <v>98553589</v>
       </c>
       <c r="B7" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6431</v>
+        <v>779</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1314,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492844.1693733748</v>
+        <v>492694</v>
       </c>
       <c r="R7" t="n">
-        <v>6430460.621686823</v>
+        <v>6430457</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,21 +1273,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1373,7 +1289,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>lind</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98553717</v>
+        <v>97730474</v>
       </c>
       <c r="B8" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,37 +1322,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1114</v>
+        <v>805</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Restad, Sm</t>
+          <t>1201, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492758.1919310464</v>
+        <v>492778</v>
       </c>
       <c r="R8" t="n">
-        <v>6430463.425538279</v>
+        <v>6430457</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,22 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,21 +1401,16 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>ek död</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1516,15 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98554300</v>
+        <v>98553602</v>
       </c>
       <c r="B9" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492726.2984024759</v>
+        <v>492708</v>
       </c>
       <c r="R9" t="n">
-        <v>6430436.995733039</v>
+        <v>6430457</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1589,21 +1489,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1615,7 +1505,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>lind</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1637,37 +1527,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98554101</v>
+        <v>98553603</v>
       </c>
       <c r="B10" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>311</v>
+        <v>1114</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1677,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492715.9877712089</v>
+        <v>492702</v>
       </c>
       <c r="R10" t="n">
-        <v>6430313.049289712</v>
+        <v>6430455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1710,21 +1595,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1736,7 +1611,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>lind</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1758,37 +1633,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98554404</v>
+        <v>98553604</v>
       </c>
       <c r="B11" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>1114</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1798,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492729.0139582447</v>
+        <v>492694</v>
       </c>
       <c r="R11" t="n">
-        <v>6430470.895141605</v>
+        <v>6430457</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1831,21 +1701,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1857,7 +1717,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>aspved</t>
+          <t>lind</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1879,37 +1739,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98553632</v>
+        <v>98553605</v>
       </c>
       <c r="B12" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1114</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1919,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492673.3480776717</v>
+        <v>492686</v>
       </c>
       <c r="R12" t="n">
-        <v>6430505.430762033</v>
+        <v>6430458</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1952,21 +1807,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1978,7 +1823,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>lind</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,15 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98553604</v>
+        <v>98553606</v>
       </c>
       <c r="B13" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492693.9580591197</v>
+        <v>492681</v>
       </c>
       <c r="R13" t="n">
-        <v>6430456.655794837</v>
+        <v>6430458</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2073,19 +1913,9 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,15 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98554297</v>
+        <v>98553657</v>
       </c>
       <c r="B14" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492712.3613437378</v>
+        <v>492674</v>
       </c>
       <c r="R14" t="n">
-        <v>6430361.794840507</v>
+        <v>6430506</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2194,21 +2019,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2220,7 +2035,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>lönn</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2242,15 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98553657</v>
+        <v>98553658</v>
       </c>
       <c r="B15" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492673.3480776717</v>
+        <v>492678</v>
       </c>
       <c r="R15" t="n">
-        <v>6430505.430762033</v>
+        <v>6430510</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2315,19 +2125,9 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2363,15 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98553605</v>
+        <v>98553659</v>
       </c>
       <c r="B16" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492686.0006148596</v>
+        <v>492727</v>
       </c>
       <c r="R16" t="n">
-        <v>6430458.789389904</v>
+        <v>6430497</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2436,21 +2231,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2462,7 +2247,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>lind</t>
+          <t>lönn</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,37 +2269,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98554739</v>
+        <v>98553660</v>
       </c>
       <c r="B17" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6431</v>
+        <v>1114</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2524,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492683.4012255681</v>
+        <v>492782</v>
       </c>
       <c r="R17" t="n">
-        <v>6430488.460322117</v>
+        <v>6430482</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2557,21 +2337,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2583,7 +2353,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>alm</t>
+          <t>lönn</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2605,37 +2375,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98553589</v>
+        <v>98553661</v>
       </c>
       <c r="B18" t="n">
-        <v>81326</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>779</v>
+        <v>1114</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2645,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492693.9580591197</v>
+        <v>492805</v>
       </c>
       <c r="R18" t="n">
-        <v>6430456.655794837</v>
+        <v>6430474</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2678,21 +2443,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2704,7 +2459,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>lind</t>
+          <t>lönn</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,15 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98553658</v>
+        <v>98553717</v>
       </c>
       <c r="B19" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,10 +2516,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492678.6652824333</v>
+        <v>492758</v>
       </c>
       <c r="R19" t="n">
-        <v>6430510.718488825</v>
+        <v>6430464</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2799,21 +2549,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2825,7 +2565,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>ek död</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2847,15 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98554302</v>
+        <v>98554295</v>
       </c>
       <c r="B20" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492741.6653291934</v>
+        <v>492714</v>
       </c>
       <c r="R20" t="n">
-        <v>6430423.194030191</v>
+        <v>6430361</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2920,19 +2655,9 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2968,15 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98554295</v>
+        <v>98554297</v>
       </c>
       <c r="B21" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492713.9526799888</v>
+        <v>492712</v>
       </c>
       <c r="R21" t="n">
-        <v>6430361.262167387</v>
+        <v>6430362</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3041,19 +2761,9 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3089,15 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98553603</v>
+        <v>98554300</v>
       </c>
       <c r="B22" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492701.91648055</v>
+        <v>492726</v>
       </c>
       <c r="R22" t="n">
-        <v>6430455.051968228</v>
+        <v>6430437</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3162,21 +2867,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3188,7 +2883,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>lind</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3210,37 +2905,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>98553626</v>
+        <v>98554302</v>
       </c>
       <c r="B23" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6431</v>
+        <v>1114</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3250,10 +2940,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492706.2467511788</v>
+        <v>492741</v>
       </c>
       <c r="R23" t="n">
-        <v>6430501.132510502</v>
+        <v>6430423</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3283,21 +2973,11 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3309,7 +2989,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3331,53 +3011,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98553602</v>
+        <v>97730476</v>
       </c>
       <c r="B24" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1114</v>
+        <v>1458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Restad, Sm</t>
+          <t>1201, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492708.2894165414</v>
+        <v>492704</v>
       </c>
       <c r="R24" t="n">
-        <v>6430457.159341051</v>
+        <v>6430349</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3401,22 +3085,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,21 +3101,16 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>lind</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3455,12 +3124,7 @@
         <v>98554732</v>
       </c>
       <c r="B25" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3482,7 +3146,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3492,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492681.79245941</v>
+        <v>492682</v>
       </c>
       <c r="R25" t="n">
-        <v>6430479.457493982</v>
+        <v>6430480</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3525,19 +3189,9 @@
           <t>2022-01-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3566,6 +3220,1162 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97730472</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1201, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>492738</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6430482</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>97730473</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1201, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>492727</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6430461</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>98554404</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>492729</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6430471</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>aspved</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>98553626</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>492707</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6430501</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>98553627</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>492844</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6430460</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>98554739</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>492684</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6430489</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>alm</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>98553630</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>492656</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6430511</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>98553631</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>492668</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6430508</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>98553632</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>492674</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6430506</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>98553633</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>492805</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6430475</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstF Lövskogsinventering 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>98553629</v>
+      </c>
+      <c r="B36" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Restad, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>492807</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6430475</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
         <is>
           <t>LstF Lövskogsinventering 2021</t>
         </is>

--- a/artfynd/A 10495-2026 artfynd.xlsx
+++ b/artfynd/A 10495-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553592</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554094</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554106</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554109</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553589</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730474</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553602</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553603</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553604</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553605</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553606</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553657</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553658</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2266,6 +2341,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553659</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,6 +2452,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553660</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2478,6 +2563,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553661</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2584,6 +2674,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553717</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2690,6 +2785,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554295</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2796,6 +2896,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554297</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2902,6 +3007,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554300</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3008,6 +3118,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554302</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3118,6 +3233,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730476</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3224,6 +3344,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554732</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3325,6 +3450,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730472</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3426,6 +3556,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730473</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3532,6 +3667,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554404</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3638,6 +3778,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553626</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3744,6 +3889,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3850,6 +4000,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554739</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3956,6 +4111,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553630</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4062,6 +4222,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553631</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4168,6 +4333,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553632</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4274,6 +4444,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553633</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4380,8 +4555,50 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>